--- a/data/attendance/ECOLE_فردي_تسيير_واقتصاد.xlsx
+++ b/data/attendance/ECOLE_فردي_تسيير_واقتصاد.xlsx
@@ -1,217 +1,216 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30430"/>
-  <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B88B6504-5A5F-4C18-82EE-641049F5A791}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720"/>
   </bookViews>
   <sheets>
-    <sheet name="Présences" sheetId="1" r:id="rId1"/>
-    <sheet name="📖 Instructions" sheetId="2" r:id="rId2"/>
+    <sheet sheetId="1" name="Présences" state="visible" r:id="rId4"/>
+    <sheet sheetId="2" name="📖 Instructions" state="visible" r:id="rId5"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>Author</author>
   </authors>
   <commentList>
-    <comment ref="B5" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
+    <comment ref="B5" authorId="0">
       <text>
         <r>
           <rPr>
-            <sz val="11"/>
             <color theme="1"/>
-            <rFont val="Calibri"/>
             <family val="2"/>
             <scheme val="minor"/>
+            <sz val="11"/>
+            <rFont val="Calibri"/>
           </rPr>
           <t>student_id:2aeae84b-7384-401e-8647-7df577c4d20a</t>
         </r>
       </text>
     </comment>
-    <comment ref="B6" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
+    <comment ref="B6" authorId="0">
       <text>
         <r>
           <rPr>
-            <sz val="11"/>
             <color theme="1"/>
-            <rFont val="Calibri"/>
             <family val="2"/>
             <scheme val="minor"/>
+            <sz val="11"/>
+            <rFont val="Calibri"/>
           </rPr>
           <t>student_id:8110f642-6ccc-4338-a49d-9adac692b370</t>
         </r>
       </text>
     </comment>
-    <comment ref="B7" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000003000000}">
+    <comment ref="B7" authorId="0">
       <text>
         <r>
           <rPr>
-            <sz val="11"/>
             <color theme="1"/>
-            <rFont val="Calibri"/>
             <family val="2"/>
             <scheme val="minor"/>
+            <sz val="11"/>
+            <rFont val="Calibri"/>
           </rPr>
           <t>student_id:39d65e7b-c3dc-4763-b297-23e913a2b8fa</t>
         </r>
       </text>
     </comment>
-    <comment ref="B8" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000004000000}">
+    <comment ref="B8" authorId="0">
       <text>
         <r>
           <rPr>
-            <sz val="11"/>
             <color theme="1"/>
-            <rFont val="Calibri"/>
             <family val="2"/>
             <scheme val="minor"/>
+            <sz val="11"/>
+            <rFont val="Calibri"/>
           </rPr>
           <t>student_id:aa28d84b-d2d0-4e49-b7a5-75651a7c90b8</t>
         </r>
       </text>
     </comment>
-    <comment ref="B9" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000005000000}">
+    <comment ref="B9" authorId="0">
       <text>
         <r>
           <rPr>
-            <sz val="11"/>
             <color theme="1"/>
-            <rFont val="Calibri"/>
             <family val="2"/>
             <scheme val="minor"/>
+            <sz val="11"/>
+            <rFont val="Calibri"/>
           </rPr>
           <t>student_id:13496a46-b51f-4d72-bbae-de60607efd62</t>
         </r>
       </text>
     </comment>
-    <comment ref="B10" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000006000000}">
+    <comment ref="B10" authorId="0">
       <text>
         <r>
           <rPr>
-            <sz val="11"/>
             <color theme="1"/>
-            <rFont val="Calibri"/>
             <family val="2"/>
             <scheme val="minor"/>
+            <sz val="11"/>
+            <rFont val="Calibri"/>
           </rPr>
           <t>student_id:7c846c49-a305-40f9-9a3f-2de2c726b307</t>
         </r>
       </text>
     </comment>
-    <comment ref="B11" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000007000000}">
+    <comment ref="B11" authorId="0">
       <text>
         <r>
           <rPr>
-            <sz val="11"/>
             <color theme="1"/>
-            <rFont val="Calibri"/>
             <family val="2"/>
             <scheme val="minor"/>
+            <sz val="11"/>
+            <rFont val="Calibri"/>
           </rPr>
           <t>student_id:17982247-f786-4822-af3f-af72c5b887f3</t>
         </r>
       </text>
     </comment>
-    <comment ref="B12" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000008000000}">
+    <comment ref="B12" authorId="0">
       <text>
         <r>
           <rPr>
-            <sz val="11"/>
             <color theme="1"/>
-            <rFont val="Calibri"/>
             <family val="2"/>
             <scheme val="minor"/>
+            <sz val="11"/>
+            <rFont val="Calibri"/>
           </rPr>
           <t>student_id:d9c5675f-1cc4-42b7-b8f1-c384b2a68732</t>
         </r>
       </text>
     </comment>
-    <comment ref="B13" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000009000000}">
+    <comment ref="B13" authorId="0">
       <text>
         <r>
           <rPr>
-            <sz val="11"/>
             <color theme="1"/>
-            <rFont val="Calibri"/>
             <family val="2"/>
             <scheme val="minor"/>
+            <sz val="11"/>
+            <rFont val="Calibri"/>
           </rPr>
           <t>student_id:4d9dda30-0de3-4b72-9f91-dcf83face32a</t>
         </r>
       </text>
     </comment>
-    <comment ref="B14" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000A000000}">
+    <comment ref="B14" authorId="0">
       <text>
         <r>
           <rPr>
-            <sz val="11"/>
             <color theme="1"/>
-            <rFont val="Calibri"/>
             <family val="2"/>
             <scheme val="minor"/>
+            <sz val="11"/>
+            <rFont val="Calibri"/>
           </rPr>
           <t>student_id:4bfab05d-be25-4991-9c76-6462daa13294</t>
         </r>
       </text>
     </comment>
-    <comment ref="B15" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000B000000}">
+    <comment ref="B15" authorId="0">
       <text>
         <r>
           <rPr>
-            <sz val="11"/>
             <color theme="1"/>
-            <rFont val="Calibri"/>
             <family val="2"/>
             <scheme val="minor"/>
+            <sz val="11"/>
+            <rFont val="Calibri"/>
           </rPr>
           <t>student_id:cc02d1cc-90e6-4a4c-9461-9465e15ab997</t>
         </r>
       </text>
     </comment>
-    <comment ref="B16" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000C000000}">
+    <comment ref="B16" authorId="0">
       <text>
         <r>
           <rPr>
-            <sz val="11"/>
             <color theme="1"/>
-            <rFont val="Calibri"/>
             <family val="2"/>
             <scheme val="minor"/>
+            <sz val="11"/>
+            <rFont val="Calibri"/>
           </rPr>
           <t>student_id:1d3abdfb-674e-4619-95a1-2758df484f39</t>
         </r>
       </text>
     </comment>
-    <comment ref="B17" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000D000000}">
+    <comment ref="B17" authorId="0">
       <text>
         <r>
           <rPr>
-            <sz val="11"/>
             <color theme="1"/>
-            <rFont val="Calibri"/>
             <family val="2"/>
             <scheme val="minor"/>
+            <sz val="11"/>
+            <rFont val="Calibri"/>
           </rPr>
           <t>student_id:3f6d2f5e-4850-4093-903e-1edc6207e0e1</t>
         </r>
       </text>
     </comment>
-    <comment ref="B18" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000E000000}">
+    <comment ref="B18" authorId="0">
       <text>
         <r>
           <rPr>
-            <sz val="11"/>
             <color theme="1"/>
-            <rFont val="Calibri"/>
             <family val="2"/>
             <scheme val="minor"/>
+            <sz val="11"/>
+            <rFont val="Calibri"/>
           </rPr>
           <t>student_id:6b97d4d0-c34f-44f3-90a3-d30256fd6830</t>
         </r>
@@ -245,6 +244,15 @@
     <t>الاسم واللقب</t>
   </si>
   <si>
+    <t>19/09/2026</t>
+  </si>
+  <si>
+    <t>26/09/2026</t>
+  </si>
+  <si>
+    <t>29/09/2026</t>
+  </si>
+  <si>
     <t/>
   </si>
   <si>
@@ -321,56 +329,47 @@
   </si>
   <si>
     <t>4. احفظ الملف (Ctrl+S) بعد الانتهاء ثم شغّل أمر الاستيراد.</t>
-  </si>
-  <si>
-    <t>19/9/2026</t>
-  </si>
-  <si>
-    <t>26/9/2026</t>
-  </si>
-  <si>
-    <t>29/09/2026</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="8" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
       <name val="Calibri"/>
     </font>
     <font>
       <b/>
-      <sz val="9"/>
-      <color rgb="FFC00000"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="13"/>
       <name val="Calibri"/>
     </font>
     <font>
       <b/>
-      <sz val="10"/>
       <color rgb="FFC00000"/>
+      <sz val="9"/>
       <name val="Calibri"/>
     </font>
     <font>
       <b/>
+      <color rgb="FFC00000"/>
       <sz val="10"/>
-      <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
     </font>
     <font>
+      <b/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="10"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <color rgb="FF666666"/>
       <sz val="9"/>
-      <color rgb="FF666666"/>
       <name val="Calibri"/>
     </font>
     <font>
@@ -456,13 +455,19 @@
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -478,12 +483,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -822,34 +821,34 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:N18"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
     <col min="2" max="2" width="30" customWidth="1"/>
     <col min="3" max="14" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
-      <c r="F1" s="9"/>
-      <c r="G1" s="9"/>
-      <c r="H1" s="9"/>
-      <c r="I1" s="9"/>
-      <c r="J1" s="9"/>
-      <c r="K1" s="9"/>
-      <c r="L1" s="9"/>
-      <c r="M1" s="9"/>
-      <c r="N1" s="9"/>
-    </row>
-    <row r="2" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1" ht="27.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1"/>
+    </row>
+    <row r="2" hidden="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -860,705 +859,705 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="10" t="s">
+    <row r="3" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="10"/>
-      <c r="C3" s="1">
-        <v>0</v>
-      </c>
-      <c r="D3" s="1">
-        <v>0</v>
-      </c>
-      <c r="E3" s="1">
-        <v>0</v>
-      </c>
-      <c r="F3" s="1">
-        <v>0</v>
-      </c>
-      <c r="G3" s="1">
-        <v>0</v>
-      </c>
-      <c r="H3" s="1">
-        <v>0</v>
-      </c>
-      <c r="I3" s="1">
-        <v>0</v>
-      </c>
-      <c r="J3" s="1">
-        <v>0</v>
-      </c>
-      <c r="K3" s="1">
-        <v>0</v>
-      </c>
-      <c r="L3" s="1">
-        <v>0</v>
-      </c>
-      <c r="M3" s="1">
-        <v>0</v>
-      </c>
-      <c r="N3" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14" ht="42" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
+      <c r="B3" s="2"/>
+      <c r="C3" s="3">
+        <v>0</v>
+      </c>
+      <c r="D3" s="3">
+        <v>0</v>
+      </c>
+      <c r="E3" s="3">
+        <v>0</v>
+      </c>
+      <c r="F3" s="3">
+        <v>0</v>
+      </c>
+      <c r="G3" s="3">
+        <v>0</v>
+      </c>
+      <c r="H3" s="3">
+        <v>0</v>
+      </c>
+      <c r="I3" s="3">
+        <v>0</v>
+      </c>
+      <c r="J3" s="3">
+        <v>0</v>
+      </c>
+      <c r="K3" s="3">
+        <v>0</v>
+      </c>
+      <c r="L3" s="3">
+        <v>0</v>
+      </c>
+      <c r="M3" s="3">
+        <v>0</v>
+      </c>
+      <c r="N3" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" ht="42" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A4" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="F4" s="3" t="s">
+      <c r="C4" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="G4" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="I4" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="J4" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="K4" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="L4" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="M4" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="N4" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="4">
+      <c r="D4" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="G4" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="H4" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="I4" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="J4" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="K4" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="L4" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="M4" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="N4" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" ht="18.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A5" s="6">
         <v>417</v>
       </c>
-      <c r="B5" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C5" s="6">
-        <v>1</v>
-      </c>
-      <c r="D5" s="6">
-        <v>1</v>
-      </c>
-      <c r="E5" s="6">
-        <v>0</v>
-      </c>
-      <c r="F5" s="6">
-        <v>0</v>
-      </c>
-      <c r="G5" s="6">
-        <v>0</v>
-      </c>
-      <c r="H5" s="6">
-        <v>0</v>
-      </c>
-      <c r="I5" s="6">
-        <v>0</v>
-      </c>
-      <c r="J5" s="6">
-        <v>0</v>
-      </c>
-      <c r="K5" s="6">
-        <v>0</v>
-      </c>
-      <c r="L5" s="6">
-        <v>0</v>
-      </c>
-      <c r="M5" s="6">
-        <v>0</v>
-      </c>
-      <c r="N5" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="4">
+      <c r="B5" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" s="8">
+        <v>1</v>
+      </c>
+      <c r="D5" s="8">
+        <v>1</v>
+      </c>
+      <c r="E5" s="8">
+        <v>0</v>
+      </c>
+      <c r="F5" s="8">
+        <v>0</v>
+      </c>
+      <c r="G5" s="8">
+        <v>0</v>
+      </c>
+      <c r="H5" s="8">
+        <v>0</v>
+      </c>
+      <c r="I5" s="8">
+        <v>0</v>
+      </c>
+      <c r="J5" s="8">
+        <v>0</v>
+      </c>
+      <c r="K5" s="8">
+        <v>0</v>
+      </c>
+      <c r="L5" s="8">
+        <v>0</v>
+      </c>
+      <c r="M5" s="8">
+        <v>0</v>
+      </c>
+      <c r="N5" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" ht="18.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A6" s="6">
         <v>418</v>
       </c>
-      <c r="B6" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C6" s="7">
-        <v>1</v>
-      </c>
-      <c r="D6" s="7">
-        <v>1</v>
-      </c>
-      <c r="E6" s="7">
-        <v>1</v>
-      </c>
-      <c r="F6" s="7">
-        <v>0</v>
-      </c>
-      <c r="G6" s="7">
-        <v>0</v>
-      </c>
-      <c r="H6" s="7">
-        <v>0</v>
-      </c>
-      <c r="I6" s="7">
-        <v>0</v>
-      </c>
-      <c r="J6" s="7">
-        <v>0</v>
-      </c>
-      <c r="K6" s="7">
-        <v>0</v>
-      </c>
-      <c r="L6" s="7">
-        <v>0</v>
-      </c>
-      <c r="M6" s="7">
-        <v>0</v>
-      </c>
-      <c r="N6" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="4">
+      <c r="B6" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" s="9">
+        <v>1</v>
+      </c>
+      <c r="D6" s="9">
+        <v>1</v>
+      </c>
+      <c r="E6" s="9">
+        <v>1</v>
+      </c>
+      <c r="F6" s="9">
+        <v>0</v>
+      </c>
+      <c r="G6" s="9">
+        <v>0</v>
+      </c>
+      <c r="H6" s="9">
+        <v>0</v>
+      </c>
+      <c r="I6" s="9">
+        <v>0</v>
+      </c>
+      <c r="J6" s="9">
+        <v>0</v>
+      </c>
+      <c r="K6" s="9">
+        <v>0</v>
+      </c>
+      <c r="L6" s="9">
+        <v>0</v>
+      </c>
+      <c r="M6" s="9">
+        <v>0</v>
+      </c>
+      <c r="N6" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" ht="18.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A7" s="6">
         <v>424</v>
       </c>
-      <c r="B7" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C7" s="6">
-        <v>1</v>
-      </c>
-      <c r="D7" s="6">
-        <v>1</v>
-      </c>
-      <c r="E7" s="6">
-        <v>0</v>
-      </c>
-      <c r="F7" s="6">
-        <v>0</v>
-      </c>
-      <c r="G7" s="6">
-        <v>0</v>
-      </c>
-      <c r="H7" s="6">
-        <v>0</v>
-      </c>
-      <c r="I7" s="6">
-        <v>0</v>
-      </c>
-      <c r="J7" s="6">
-        <v>0</v>
-      </c>
-      <c r="K7" s="6">
-        <v>0</v>
-      </c>
-      <c r="L7" s="6">
-        <v>0</v>
-      </c>
-      <c r="M7" s="6">
-        <v>0</v>
-      </c>
-      <c r="N7" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="4">
+      <c r="B7" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="C7" s="8">
+        <v>1</v>
+      </c>
+      <c r="D7" s="8">
+        <v>1</v>
+      </c>
+      <c r="E7" s="8">
+        <v>0</v>
+      </c>
+      <c r="F7" s="8">
+        <v>0</v>
+      </c>
+      <c r="G7" s="8">
+        <v>0</v>
+      </c>
+      <c r="H7" s="8">
+        <v>0</v>
+      </c>
+      <c r="I7" s="8">
+        <v>0</v>
+      </c>
+      <c r="J7" s="8">
+        <v>0</v>
+      </c>
+      <c r="K7" s="8">
+        <v>0</v>
+      </c>
+      <c r="L7" s="8">
+        <v>0</v>
+      </c>
+      <c r="M7" s="8">
+        <v>0</v>
+      </c>
+      <c r="N7" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" ht="18.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A8" s="6">
         <v>427</v>
       </c>
-      <c r="B8" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C8" s="7">
-        <v>1</v>
-      </c>
-      <c r="D8" s="7">
-        <v>1</v>
-      </c>
-      <c r="E8" s="7">
-        <v>1</v>
-      </c>
-      <c r="F8" s="7">
-        <v>0</v>
-      </c>
-      <c r="G8" s="7">
-        <v>0</v>
-      </c>
-      <c r="H8" s="7">
-        <v>0</v>
-      </c>
-      <c r="I8" s="7">
-        <v>0</v>
-      </c>
-      <c r="J8" s="7">
-        <v>0</v>
-      </c>
-      <c r="K8" s="7">
-        <v>0</v>
-      </c>
-      <c r="L8" s="7">
-        <v>0</v>
-      </c>
-      <c r="M8" s="7">
-        <v>0</v>
-      </c>
-      <c r="N8" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="4">
+      <c r="B8" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C8" s="9">
+        <v>1</v>
+      </c>
+      <c r="D8" s="9">
+        <v>1</v>
+      </c>
+      <c r="E8" s="9">
+        <v>1</v>
+      </c>
+      <c r="F8" s="9">
+        <v>0</v>
+      </c>
+      <c r="G8" s="9">
+        <v>0</v>
+      </c>
+      <c r="H8" s="9">
+        <v>0</v>
+      </c>
+      <c r="I8" s="9">
+        <v>0</v>
+      </c>
+      <c r="J8" s="9">
+        <v>0</v>
+      </c>
+      <c r="K8" s="9">
+        <v>0</v>
+      </c>
+      <c r="L8" s="9">
+        <v>0</v>
+      </c>
+      <c r="M8" s="9">
+        <v>0</v>
+      </c>
+      <c r="N8" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" ht="18.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A9" s="6">
         <v>589</v>
       </c>
-      <c r="B9" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C9" s="6">
-        <v>1</v>
-      </c>
-      <c r="D9" s="6">
-        <v>1</v>
-      </c>
-      <c r="E9" s="6">
-        <v>1</v>
-      </c>
-      <c r="F9" s="6">
-        <v>0</v>
-      </c>
-      <c r="G9" s="6">
-        <v>0</v>
-      </c>
-      <c r="H9" s="6">
-        <v>0</v>
-      </c>
-      <c r="I9" s="6">
-        <v>0</v>
-      </c>
-      <c r="J9" s="6">
-        <v>0</v>
-      </c>
-      <c r="K9" s="6">
-        <v>0</v>
-      </c>
-      <c r="L9" s="6">
-        <v>0</v>
-      </c>
-      <c r="M9" s="6">
-        <v>0</v>
-      </c>
-      <c r="N9" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="4">
+      <c r="B9" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="C9" s="8">
+        <v>1</v>
+      </c>
+      <c r="D9" s="8">
+        <v>1</v>
+      </c>
+      <c r="E9" s="8">
+        <v>1</v>
+      </c>
+      <c r="F9" s="8">
+        <v>0</v>
+      </c>
+      <c r="G9" s="8">
+        <v>0</v>
+      </c>
+      <c r="H9" s="8">
+        <v>0</v>
+      </c>
+      <c r="I9" s="8">
+        <v>0</v>
+      </c>
+      <c r="J9" s="8">
+        <v>0</v>
+      </c>
+      <c r="K9" s="8">
+        <v>0</v>
+      </c>
+      <c r="L9" s="8">
+        <v>0</v>
+      </c>
+      <c r="M9" s="8">
+        <v>0</v>
+      </c>
+      <c r="N9" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" ht="18.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A10" s="6">
         <v>709</v>
       </c>
-      <c r="B10" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C10" s="7">
-        <v>0</v>
-      </c>
-      <c r="D10" s="7">
-        <v>0</v>
-      </c>
-      <c r="E10" s="7">
-        <v>1</v>
-      </c>
-      <c r="F10" s="7">
-        <v>0</v>
-      </c>
-      <c r="G10" s="7">
-        <v>0</v>
-      </c>
-      <c r="H10" s="7">
-        <v>0</v>
-      </c>
-      <c r="I10" s="7">
-        <v>0</v>
-      </c>
-      <c r="J10" s="7">
-        <v>0</v>
-      </c>
-      <c r="K10" s="7">
-        <v>0</v>
-      </c>
-      <c r="L10" s="7">
-        <v>0</v>
-      </c>
-      <c r="M10" s="7">
-        <v>0</v>
-      </c>
-      <c r="N10" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="4">
+      <c r="B10" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C10" s="9">
+        <v>0</v>
+      </c>
+      <c r="D10" s="9">
+        <v>0</v>
+      </c>
+      <c r="E10" s="9">
+        <v>1</v>
+      </c>
+      <c r="F10" s="9">
+        <v>0</v>
+      </c>
+      <c r="G10" s="9">
+        <v>0</v>
+      </c>
+      <c r="H10" s="9">
+        <v>0</v>
+      </c>
+      <c r="I10" s="9">
+        <v>0</v>
+      </c>
+      <c r="J10" s="9">
+        <v>0</v>
+      </c>
+      <c r="K10" s="9">
+        <v>0</v>
+      </c>
+      <c r="L10" s="9">
+        <v>0</v>
+      </c>
+      <c r="M10" s="9">
+        <v>0</v>
+      </c>
+      <c r="N10" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" ht="18.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A11" s="6">
         <v>710</v>
       </c>
-      <c r="B11" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="C11" s="6">
-        <v>1</v>
-      </c>
-      <c r="D11" s="6">
-        <v>1</v>
-      </c>
-      <c r="E11" s="6">
-        <v>0</v>
-      </c>
-      <c r="F11" s="6">
-        <v>0</v>
-      </c>
-      <c r="G11" s="6">
-        <v>0</v>
-      </c>
-      <c r="H11" s="6">
-        <v>0</v>
-      </c>
-      <c r="I11" s="6">
-        <v>0</v>
-      </c>
-      <c r="J11" s="6">
-        <v>0</v>
-      </c>
-      <c r="K11" s="6">
-        <v>0</v>
-      </c>
-      <c r="L11" s="6">
-        <v>0</v>
-      </c>
-      <c r="M11" s="6">
-        <v>0</v>
-      </c>
-      <c r="N11" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="4">
+      <c r="B11" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C11" s="8">
+        <v>1</v>
+      </c>
+      <c r="D11" s="8">
+        <v>1</v>
+      </c>
+      <c r="E11" s="8">
+        <v>0</v>
+      </c>
+      <c r="F11" s="8">
+        <v>0</v>
+      </c>
+      <c r="G11" s="8">
+        <v>0</v>
+      </c>
+      <c r="H11" s="8">
+        <v>0</v>
+      </c>
+      <c r="I11" s="8">
+        <v>0</v>
+      </c>
+      <c r="J11" s="8">
+        <v>0</v>
+      </c>
+      <c r="K11" s="8">
+        <v>0</v>
+      </c>
+      <c r="L11" s="8">
+        <v>0</v>
+      </c>
+      <c r="M11" s="8">
+        <v>0</v>
+      </c>
+      <c r="N11" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" ht="18.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A12" s="6">
         <v>711</v>
       </c>
-      <c r="B12" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="C12" s="7">
-        <v>1</v>
-      </c>
-      <c r="D12" s="7">
-        <v>1</v>
-      </c>
-      <c r="E12" s="7">
-        <v>1</v>
-      </c>
-      <c r="F12" s="7">
-        <v>0</v>
-      </c>
-      <c r="G12" s="7">
-        <v>0</v>
-      </c>
-      <c r="H12" s="7">
-        <v>0</v>
-      </c>
-      <c r="I12" s="7">
-        <v>0</v>
-      </c>
-      <c r="J12" s="7">
-        <v>0</v>
-      </c>
-      <c r="K12" s="7">
-        <v>0</v>
-      </c>
-      <c r="L12" s="7">
-        <v>0</v>
-      </c>
-      <c r="M12" s="7">
-        <v>0</v>
-      </c>
-      <c r="N12" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="4">
+      <c r="B12" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C12" s="9">
+        <v>1</v>
+      </c>
+      <c r="D12" s="9">
+        <v>1</v>
+      </c>
+      <c r="E12" s="9">
+        <v>1</v>
+      </c>
+      <c r="F12" s="9">
+        <v>0</v>
+      </c>
+      <c r="G12" s="9">
+        <v>0</v>
+      </c>
+      <c r="H12" s="9">
+        <v>0</v>
+      </c>
+      <c r="I12" s="9">
+        <v>0</v>
+      </c>
+      <c r="J12" s="9">
+        <v>0</v>
+      </c>
+      <c r="K12" s="9">
+        <v>0</v>
+      </c>
+      <c r="L12" s="9">
+        <v>0</v>
+      </c>
+      <c r="M12" s="9">
+        <v>0</v>
+      </c>
+      <c r="N12" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" ht="18.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A13" s="6">
         <v>712</v>
       </c>
-      <c r="B13" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="C13" s="6">
-        <v>0</v>
-      </c>
-      <c r="D13" s="6">
-        <v>1</v>
-      </c>
-      <c r="E13" s="6">
-        <v>1</v>
-      </c>
-      <c r="F13" s="6">
-        <v>0</v>
-      </c>
-      <c r="G13" s="6">
-        <v>0</v>
-      </c>
-      <c r="H13" s="6">
-        <v>0</v>
-      </c>
-      <c r="I13" s="6">
-        <v>0</v>
-      </c>
-      <c r="J13" s="6">
-        <v>0</v>
-      </c>
-      <c r="K13" s="6">
-        <v>0</v>
-      </c>
-      <c r="L13" s="6">
-        <v>0</v>
-      </c>
-      <c r="M13" s="6">
-        <v>0</v>
-      </c>
-      <c r="N13" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="4">
+      <c r="B13" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="C13" s="8">
+        <v>0</v>
+      </c>
+      <c r="D13" s="8">
+        <v>1</v>
+      </c>
+      <c r="E13" s="8">
+        <v>1</v>
+      </c>
+      <c r="F13" s="8">
+        <v>0</v>
+      </c>
+      <c r="G13" s="8">
+        <v>0</v>
+      </c>
+      <c r="H13" s="8">
+        <v>0</v>
+      </c>
+      <c r="I13" s="8">
+        <v>0</v>
+      </c>
+      <c r="J13" s="8">
+        <v>0</v>
+      </c>
+      <c r="K13" s="8">
+        <v>0</v>
+      </c>
+      <c r="L13" s="8">
+        <v>0</v>
+      </c>
+      <c r="M13" s="8">
+        <v>0</v>
+      </c>
+      <c r="N13" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" ht="18.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A14" s="6">
         <v>713</v>
       </c>
-      <c r="B14" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="C14" s="7">
-        <v>1</v>
-      </c>
-      <c r="D14" s="7">
-        <v>1</v>
-      </c>
-      <c r="E14" s="7">
-        <v>1</v>
-      </c>
-      <c r="F14" s="7">
-        <v>0</v>
-      </c>
-      <c r="G14" s="7">
-        <v>0</v>
-      </c>
-      <c r="H14" s="7">
-        <v>0</v>
-      </c>
-      <c r="I14" s="7">
-        <v>0</v>
-      </c>
-      <c r="J14" s="7">
-        <v>0</v>
-      </c>
-      <c r="K14" s="7">
-        <v>0</v>
-      </c>
-      <c r="L14" s="7">
-        <v>0</v>
-      </c>
-      <c r="M14" s="7">
-        <v>0</v>
-      </c>
-      <c r="N14" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="4">
+      <c r="B14" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C14" s="9">
+        <v>1</v>
+      </c>
+      <c r="D14" s="9">
+        <v>1</v>
+      </c>
+      <c r="E14" s="9">
+        <v>1</v>
+      </c>
+      <c r="F14" s="9">
+        <v>0</v>
+      </c>
+      <c r="G14" s="9">
+        <v>0</v>
+      </c>
+      <c r="H14" s="9">
+        <v>0</v>
+      </c>
+      <c r="I14" s="9">
+        <v>0</v>
+      </c>
+      <c r="J14" s="9">
+        <v>0</v>
+      </c>
+      <c r="K14" s="9">
+        <v>0</v>
+      </c>
+      <c r="L14" s="9">
+        <v>0</v>
+      </c>
+      <c r="M14" s="9">
+        <v>0</v>
+      </c>
+      <c r="N14" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" ht="18.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A15" s="6">
         <v>714</v>
       </c>
-      <c r="B15" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C15" s="6">
-        <v>0</v>
-      </c>
-      <c r="D15" s="6">
-        <v>1</v>
-      </c>
-      <c r="E15" s="6">
-        <v>1</v>
-      </c>
-      <c r="F15" s="6">
-        <v>0</v>
-      </c>
-      <c r="G15" s="6">
-        <v>0</v>
-      </c>
-      <c r="H15" s="6">
-        <v>0</v>
-      </c>
-      <c r="I15" s="6">
-        <v>0</v>
-      </c>
-      <c r="J15" s="6">
-        <v>0</v>
-      </c>
-      <c r="K15" s="6">
-        <v>0</v>
-      </c>
-      <c r="L15" s="6">
-        <v>0</v>
-      </c>
-      <c r="M15" s="6">
-        <v>0</v>
-      </c>
-      <c r="N15" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="4">
+      <c r="B15" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="C15" s="8">
+        <v>0</v>
+      </c>
+      <c r="D15" s="8">
+        <v>1</v>
+      </c>
+      <c r="E15" s="8">
+        <v>1</v>
+      </c>
+      <c r="F15" s="8">
+        <v>0</v>
+      </c>
+      <c r="G15" s="8">
+        <v>0</v>
+      </c>
+      <c r="H15" s="8">
+        <v>0</v>
+      </c>
+      <c r="I15" s="8">
+        <v>0</v>
+      </c>
+      <c r="J15" s="8">
+        <v>0</v>
+      </c>
+      <c r="K15" s="8">
+        <v>0</v>
+      </c>
+      <c r="L15" s="8">
+        <v>0</v>
+      </c>
+      <c r="M15" s="8">
+        <v>0</v>
+      </c>
+      <c r="N15" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" ht="18.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A16" s="6">
         <v>715</v>
       </c>
-      <c r="B16" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="C16" s="7">
-        <v>0</v>
-      </c>
-      <c r="D16" s="7">
-        <v>1</v>
-      </c>
-      <c r="E16" s="7">
-        <v>1</v>
-      </c>
-      <c r="F16" s="7">
-        <v>0</v>
-      </c>
-      <c r="G16" s="7">
-        <v>0</v>
-      </c>
-      <c r="H16" s="7">
-        <v>0</v>
-      </c>
-      <c r="I16" s="7">
-        <v>0</v>
-      </c>
-      <c r="J16" s="7">
-        <v>0</v>
-      </c>
-      <c r="K16" s="7">
-        <v>0</v>
-      </c>
-      <c r="L16" s="7">
-        <v>0</v>
-      </c>
-      <c r="M16" s="7">
-        <v>0</v>
-      </c>
-      <c r="N16" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:14" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="4">
+      <c r="B16" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="C16" s="9">
+        <v>0</v>
+      </c>
+      <c r="D16" s="9">
+        <v>1</v>
+      </c>
+      <c r="E16" s="9">
+        <v>1</v>
+      </c>
+      <c r="F16" s="9">
+        <v>0</v>
+      </c>
+      <c r="G16" s="9">
+        <v>0</v>
+      </c>
+      <c r="H16" s="9">
+        <v>0</v>
+      </c>
+      <c r="I16" s="9">
+        <v>0</v>
+      </c>
+      <c r="J16" s="9">
+        <v>0</v>
+      </c>
+      <c r="K16" s="9">
+        <v>0</v>
+      </c>
+      <c r="L16" s="9">
+        <v>0</v>
+      </c>
+      <c r="M16" s="9">
+        <v>0</v>
+      </c>
+      <c r="N16" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" ht="18.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A17" s="6">
         <v>716</v>
       </c>
-      <c r="B17" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="C17" s="6">
-        <v>0</v>
-      </c>
-      <c r="D17" s="6">
-        <v>1</v>
-      </c>
-      <c r="E17" s="6">
-        <v>1</v>
-      </c>
-      <c r="F17" s="6">
-        <v>0</v>
-      </c>
-      <c r="G17" s="6">
-        <v>0</v>
-      </c>
-      <c r="H17" s="6">
-        <v>0</v>
-      </c>
-      <c r="I17" s="6">
-        <v>0</v>
-      </c>
-      <c r="J17" s="6">
-        <v>0</v>
-      </c>
-      <c r="K17" s="6">
-        <v>0</v>
-      </c>
-      <c r="L17" s="6">
-        <v>0</v>
-      </c>
-      <c r="M17" s="6">
-        <v>0</v>
-      </c>
-      <c r="N17" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:14" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="4">
+      <c r="B17" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="C17" s="8">
+        <v>0</v>
+      </c>
+      <c r="D17" s="8">
+        <v>1</v>
+      </c>
+      <c r="E17" s="8">
+        <v>1</v>
+      </c>
+      <c r="F17" s="8">
+        <v>0</v>
+      </c>
+      <c r="G17" s="8">
+        <v>0</v>
+      </c>
+      <c r="H17" s="8">
+        <v>0</v>
+      </c>
+      <c r="I17" s="8">
+        <v>0</v>
+      </c>
+      <c r="J17" s="8">
+        <v>0</v>
+      </c>
+      <c r="K17" s="8">
+        <v>0</v>
+      </c>
+      <c r="L17" s="8">
+        <v>0</v>
+      </c>
+      <c r="M17" s="8">
+        <v>0</v>
+      </c>
+      <c r="N17" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" ht="18.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A18" s="6">
         <v>717</v>
       </c>
-      <c r="B18" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="C18" s="7">
-        <v>0</v>
-      </c>
-      <c r="D18" s="7">
-        <v>1</v>
-      </c>
-      <c r="E18" s="7">
-        <v>1</v>
-      </c>
-      <c r="F18" s="7">
-        <v>0</v>
-      </c>
-      <c r="G18" s="7">
-        <v>0</v>
-      </c>
-      <c r="H18" s="7">
-        <v>0</v>
-      </c>
-      <c r="I18" s="7">
-        <v>0</v>
-      </c>
-      <c r="J18" s="7">
-        <v>0</v>
-      </c>
-      <c r="K18" s="7">
-        <v>0</v>
-      </c>
-      <c r="L18" s="7">
-        <v>0</v>
-      </c>
-      <c r="M18" s="7">
-        <v>0</v>
-      </c>
-      <c r="N18" s="7">
+      <c r="B18" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C18" s="9">
+        <v>0</v>
+      </c>
+      <c r="D18" s="9">
+        <v>1</v>
+      </c>
+      <c r="E18" s="9">
+        <v>1</v>
+      </c>
+      <c r="F18" s="9">
+        <v>0</v>
+      </c>
+      <c r="G18" s="9">
+        <v>0</v>
+      </c>
+      <c r="H18" s="9">
+        <v>0</v>
+      </c>
+      <c r="I18" s="9">
+        <v>0</v>
+      </c>
+      <c r="J18" s="9">
+        <v>0</v>
+      </c>
+      <c r="K18" s="9">
+        <v>0</v>
+      </c>
+      <c r="L18" s="9">
+        <v>0</v>
+      </c>
+      <c r="M18" s="9">
+        <v>0</v>
+      </c>
+      <c r="N18" s="9">
         <v>0</v>
       </c>
     </row>
@@ -1568,99 +1567,99 @@
     <mergeCell ref="A3:B3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
-  <legacyDrawing r:id="rId1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor rgb="FF70AD47"/>
   </sheetPr>
   <dimension ref="A1:A15"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="A1" s="8" t="s">
-        <v>22</v>
+    <row r="1" ht="17.25" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1" s="10" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
--- a/data/attendance/ECOLE_فردي_تسيير_واقتصاد.xlsx
+++ b/data/attendance/ECOLE_فردي_تسيير_واقتصاد.xlsx
@@ -3,9 +3,6 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
-  <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720"/>
-  </bookViews>
   <sheets>
     <sheet sheetId="1" name="Présences" state="visible" r:id="rId4"/>
     <sheet sheetId="2" name="📖 Instructions" state="visible" r:id="rId5"/>
@@ -23,13 +20,6 @@
     <comment ref="B5" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
           <t>student_id:2aeae84b-7384-401e-8647-7df577c4d20a</t>
         </r>
       </text>
@@ -37,13 +27,6 @@
     <comment ref="B6" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
           <t>student_id:8110f642-6ccc-4338-a49d-9adac692b370</t>
         </r>
       </text>
@@ -51,13 +34,6 @@
     <comment ref="B7" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
           <t>student_id:39d65e7b-c3dc-4763-b297-23e913a2b8fa</t>
         </r>
       </text>
@@ -65,13 +41,6 @@
     <comment ref="B8" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
           <t>student_id:aa28d84b-d2d0-4e49-b7a5-75651a7c90b8</t>
         </r>
       </text>
@@ -79,13 +48,6 @@
     <comment ref="B9" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
           <t>student_id:13496a46-b51f-4d72-bbae-de60607efd62</t>
         </r>
       </text>
@@ -93,126 +55,84 @@
     <comment ref="B10" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
-          <t>student_id:7c846c49-a305-40f9-9a3f-2de2c726b307</t>
+          <t>student_id:abbb038d-e6b7-4b7f-a6d2-6da0ce2ed84c</t>
         </r>
       </text>
     </comment>
     <comment ref="B11" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
-          <t>student_id:17982247-f786-4822-af3f-af72c5b887f3</t>
+          <t>student_id:7c846c49-a305-40f9-9a3f-2de2c726b307</t>
         </r>
       </text>
     </comment>
     <comment ref="B12" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
-          <t>student_id:d9c5675f-1cc4-42b7-b8f1-c384b2a68732</t>
+          <t>student_id:17982247-f786-4822-af3f-af72c5b887f3</t>
         </r>
       </text>
     </comment>
     <comment ref="B13" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
-          <t>student_id:4d9dda30-0de3-4b72-9f91-dcf83face32a</t>
+          <t>student_id:d9c5675f-1cc4-42b7-b8f1-c384b2a68732</t>
         </r>
       </text>
     </comment>
     <comment ref="B14" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
-          <t>student_id:4bfab05d-be25-4991-9c76-6462daa13294</t>
+          <t>student_id:4d9dda30-0de3-4b72-9f91-dcf83face32a</t>
         </r>
       </text>
     </comment>
     <comment ref="B15" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
-          <t>student_id:cc02d1cc-90e6-4a4c-9461-9465e15ab997</t>
+          <t>student_id:4bfab05d-be25-4991-9c76-6462daa13294</t>
         </r>
       </text>
     </comment>
     <comment ref="B16" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
-          <t>student_id:1d3abdfb-674e-4619-95a1-2758df484f39</t>
+          <t>student_id:cc02d1cc-90e6-4a4c-9461-9465e15ab997</t>
         </r>
       </text>
     </comment>
     <comment ref="B17" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
-          <t>student_id:3f6d2f5e-4850-4093-903e-1edc6207e0e1</t>
+          <t>student_id:1d3abdfb-674e-4619-95a1-2758df484f39</t>
         </r>
       </text>
     </comment>
     <comment ref="B18" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
+          <t>student_id:3f6d2f5e-4850-4093-903e-1edc6207e0e1</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B19" authorId="0">
+      <text>
+        <r>
           <t>student_id:6b97d4d0-c34f-44f3-90a3-d30256fd6830</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B20" authorId="0">
+      <text>
+        <r>
+          <t>student_id:3eb5e573-6e0d-4f79-8336-bbfc3d811296</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B21" authorId="0">
+      <text>
+        <r>
+          <t>student_id:7c2deb15-b0ca-4c75-8bca-251363f00631</t>
         </r>
       </text>
     </comment>
@@ -221,7 +141,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="41">
   <si>
     <t>فردي تسيير واقتصاد  |  ECOLE  |  BAC  |  فردي خلود</t>
   </si>
@@ -235,6 +155,9 @@
     <t>has_books=false</t>
   </si>
   <si>
+    <t>is_formation=false</t>
+  </si>
+  <si>
     <t>حصة مجانية؟ (1 = نعم / 0 = عادية)</t>
   </si>
   <si>
@@ -271,6 +194,9 @@
     <t>معيدوش أمين</t>
   </si>
   <si>
+    <t>بوعروج حسان</t>
+  </si>
+  <si>
     <t>ثعبان انس عبدالله</t>
   </si>
   <si>
@@ -283,7 +209,7 @@
     <t>رضوان فلة سجود</t>
   </si>
   <si>
-    <t>بوعروج لؤي +محمد</t>
+    <t>بوعروج لؤي</t>
   </si>
   <si>
     <t>عرباوي عبد الرؤوف</t>
@@ -298,6 +224,12 @@
     <t>حوي جابر نور الدين</t>
   </si>
   <si>
+    <t>حملاوي لجين</t>
+  </si>
+  <si>
+    <t>سعيد تومي أمنية</t>
+  </si>
+  <si>
     <t>تعليمات ملء الحضور والكتب / Instructions</t>
   </si>
   <si>
@@ -325,7 +257,10 @@
     <t>3. للأفواج التي لها كتب (ت1 / ت2 / ت3) :</t>
   </si>
   <si>
-    <t xml:space="preserve">   → اكتب 1 في خانة الفصل إذا استلم الطالب كتابه، أو 0 إذا لم يستلم</t>
+    <t xml:space="preserve">   → للأفواج التي لها كتابان في هذا الفصل (ت1): تم توفير عمودين (كتاب 1 ت 1 و كتاب 2 ت 1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   → اكتب 1 (أو X) في خانة الكتاب إذا استلم الطالب نسخته، أو 0 إذا لم يستلم</t>
   </si>
   <si>
     <t>4. احفظ الملف (Ctrl+S) بعد الانتهاء ثم شغّل أمر الاستيراد.</t>
@@ -347,40 +282,33 @@
       <b/>
       <color rgb="FFFFFFFF"/>
       <sz val="13"/>
-      <name val="Calibri"/>
     </font>
     <font>
       <b/>
       <color rgb="FFC00000"/>
       <sz val="9"/>
-      <name val="Calibri"/>
     </font>
     <font>
       <b/>
       <color rgb="FFC00000"/>
       <sz val="10"/>
-      <name val="Calibri"/>
     </font>
     <font>
       <b/>
       <color rgb="FFFFFFFF"/>
       <sz val="10"/>
-      <name val="Calibri"/>
     </font>
     <font>
-      <color rgb="FF666666"/>
+      <color rgb="666666"/>
       <sz val="9"/>
-      <name val="Calibri"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
-      <name val="Calibri"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
-      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="9">
@@ -467,7 +395,7 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -822,15 +750,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N18"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:N21"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
     <col min="2" max="2" width="30" customWidth="1"/>
     <col min="3" max="14" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="27.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="1" ht="28" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -848,7 +776,7 @@
       <c r="M1" s="1"/>
       <c r="N1" s="1"/>
     </row>
-    <row r="2" hidden="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" hidden="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -858,10 +786,13 @@
       <c r="C2" t="s">
         <v>3</v>
       </c>
+      <c r="D2" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" s="3">
@@ -903,60 +834,60 @@
     </row>
     <row r="4" ht="42" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F4" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I4" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J4" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K4" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="L4" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M4" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="N4" s="5" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="5" ht="18.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" s="6">
         <v>417</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C5" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D5" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E5" s="8">
         <v>0</v>
@@ -989,21 +920,21 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" ht="18.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="6" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" s="6">
         <v>418</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C6" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D6" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E6" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F6" s="9">
         <v>0</v>
@@ -1033,18 +964,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" ht="18.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="7" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" s="6">
         <v>424</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C7" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D7" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E7" s="8">
         <v>0</v>
@@ -1077,21 +1008,21 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" ht="18.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="8" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" s="6">
         <v>427</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C8" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D8" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E8" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F8" s="9">
         <v>0</v>
@@ -1121,21 +1052,21 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" ht="18.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="9" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" s="6">
         <v>589</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C9" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D9" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E9" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F9" s="8">
         <v>0</v>
@@ -1165,399 +1096,531 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" ht="18.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="10" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" s="6">
+        <v>602</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C10" s="9">
+        <v>0</v>
+      </c>
+      <c r="D10" s="9">
+        <v>0</v>
+      </c>
+      <c r="E10" s="9">
+        <v>0</v>
+      </c>
+      <c r="F10" s="9">
+        <v>0</v>
+      </c>
+      <c r="G10" s="9">
+        <v>0</v>
+      </c>
+      <c r="H10" s="9">
+        <v>0</v>
+      </c>
+      <c r="I10" s="9">
+        <v>0</v>
+      </c>
+      <c r="J10" s="9">
+        <v>0</v>
+      </c>
+      <c r="K10" s="9">
+        <v>0</v>
+      </c>
+      <c r="L10" s="9">
+        <v>0</v>
+      </c>
+      <c r="M10" s="9">
+        <v>0</v>
+      </c>
+      <c r="N10" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A11" s="6">
         <v>709</v>
       </c>
-      <c r="B10" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="C10" s="9">
-        <v>0</v>
-      </c>
-      <c r="D10" s="9">
-        <v>0</v>
-      </c>
-      <c r="E10" s="9">
-        <v>1</v>
-      </c>
-      <c r="F10" s="9">
-        <v>0</v>
-      </c>
-      <c r="G10" s="9">
-        <v>0</v>
-      </c>
-      <c r="H10" s="9">
-        <v>0</v>
-      </c>
-      <c r="I10" s="9">
-        <v>0</v>
-      </c>
-      <c r="J10" s="9">
-        <v>0</v>
-      </c>
-      <c r="K10" s="9">
-        <v>0</v>
-      </c>
-      <c r="L10" s="9">
-        <v>0</v>
-      </c>
-      <c r="M10" s="9">
-        <v>0</v>
-      </c>
-      <c r="N10" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" ht="18.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A11" s="6">
+      <c r="B11" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C11" s="8">
+        <v>0</v>
+      </c>
+      <c r="D11" s="8">
+        <v>0</v>
+      </c>
+      <c r="E11" s="8">
+        <v>0</v>
+      </c>
+      <c r="F11" s="8">
+        <v>0</v>
+      </c>
+      <c r="G11" s="8">
+        <v>0</v>
+      </c>
+      <c r="H11" s="8">
+        <v>0</v>
+      </c>
+      <c r="I11" s="8">
+        <v>0</v>
+      </c>
+      <c r="J11" s="8">
+        <v>0</v>
+      </c>
+      <c r="K11" s="8">
+        <v>0</v>
+      </c>
+      <c r="L11" s="8">
+        <v>0</v>
+      </c>
+      <c r="M11" s="8">
+        <v>0</v>
+      </c>
+      <c r="N11" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A12" s="6">
         <v>710</v>
       </c>
-      <c r="B11" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C11" s="8">
-        <v>1</v>
-      </c>
-      <c r="D11" s="8">
-        <v>1</v>
-      </c>
-      <c r="E11" s="8">
-        <v>0</v>
-      </c>
-      <c r="F11" s="8">
-        <v>0</v>
-      </c>
-      <c r="G11" s="8">
-        <v>0</v>
-      </c>
-      <c r="H11" s="8">
-        <v>0</v>
-      </c>
-      <c r="I11" s="8">
-        <v>0</v>
-      </c>
-      <c r="J11" s="8">
-        <v>0</v>
-      </c>
-      <c r="K11" s="8">
-        <v>0</v>
-      </c>
-      <c r="L11" s="8">
-        <v>0</v>
-      </c>
-      <c r="M11" s="8">
-        <v>0</v>
-      </c>
-      <c r="N11" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" ht="18.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A12" s="6">
+      <c r="B12" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="C12" s="9">
+        <v>0</v>
+      </c>
+      <c r="D12" s="9">
+        <v>0</v>
+      </c>
+      <c r="E12" s="9">
+        <v>0</v>
+      </c>
+      <c r="F12" s="9">
+        <v>0</v>
+      </c>
+      <c r="G12" s="9">
+        <v>0</v>
+      </c>
+      <c r="H12" s="9">
+        <v>0</v>
+      </c>
+      <c r="I12" s="9">
+        <v>0</v>
+      </c>
+      <c r="J12" s="9">
+        <v>0</v>
+      </c>
+      <c r="K12" s="9">
+        <v>0</v>
+      </c>
+      <c r="L12" s="9">
+        <v>0</v>
+      </c>
+      <c r="M12" s="9">
+        <v>0</v>
+      </c>
+      <c r="N12" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A13" s="6">
         <v>711</v>
       </c>
-      <c r="B12" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="C12" s="9">
-        <v>1</v>
-      </c>
-      <c r="D12" s="9">
-        <v>1</v>
-      </c>
-      <c r="E12" s="9">
-        <v>1</v>
-      </c>
-      <c r="F12" s="9">
-        <v>0</v>
-      </c>
-      <c r="G12" s="9">
-        <v>0</v>
-      </c>
-      <c r="H12" s="9">
-        <v>0</v>
-      </c>
-      <c r="I12" s="9">
-        <v>0</v>
-      </c>
-      <c r="J12" s="9">
-        <v>0</v>
-      </c>
-      <c r="K12" s="9">
-        <v>0</v>
-      </c>
-      <c r="L12" s="9">
-        <v>0</v>
-      </c>
-      <c r="M12" s="9">
-        <v>0</v>
-      </c>
-      <c r="N12" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" ht="18.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A13" s="6">
+      <c r="B13" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C13" s="8">
+        <v>0</v>
+      </c>
+      <c r="D13" s="8">
+        <v>0</v>
+      </c>
+      <c r="E13" s="8">
+        <v>0</v>
+      </c>
+      <c r="F13" s="8">
+        <v>0</v>
+      </c>
+      <c r="G13" s="8">
+        <v>0</v>
+      </c>
+      <c r="H13" s="8">
+        <v>0</v>
+      </c>
+      <c r="I13" s="8">
+        <v>0</v>
+      </c>
+      <c r="J13" s="8">
+        <v>0</v>
+      </c>
+      <c r="K13" s="8">
+        <v>0</v>
+      </c>
+      <c r="L13" s="8">
+        <v>0</v>
+      </c>
+      <c r="M13" s="8">
+        <v>0</v>
+      </c>
+      <c r="N13" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A14" s="6">
         <v>712</v>
       </c>
-      <c r="B13" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="C13" s="8">
-        <v>0</v>
-      </c>
-      <c r="D13" s="8">
-        <v>1</v>
-      </c>
-      <c r="E13" s="8">
-        <v>1</v>
-      </c>
-      <c r="F13" s="8">
-        <v>0</v>
-      </c>
-      <c r="G13" s="8">
-        <v>0</v>
-      </c>
-      <c r="H13" s="8">
-        <v>0</v>
-      </c>
-      <c r="I13" s="8">
-        <v>0</v>
-      </c>
-      <c r="J13" s="8">
-        <v>0</v>
-      </c>
-      <c r="K13" s="8">
-        <v>0</v>
-      </c>
-      <c r="L13" s="8">
-        <v>0</v>
-      </c>
-      <c r="M13" s="8">
-        <v>0</v>
-      </c>
-      <c r="N13" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" ht="18.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A14" s="6">
+      <c r="B14" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="C14" s="9">
+        <v>0</v>
+      </c>
+      <c r="D14" s="9">
+        <v>0</v>
+      </c>
+      <c r="E14" s="9">
+        <v>0</v>
+      </c>
+      <c r="F14" s="9">
+        <v>0</v>
+      </c>
+      <c r="G14" s="9">
+        <v>0</v>
+      </c>
+      <c r="H14" s="9">
+        <v>0</v>
+      </c>
+      <c r="I14" s="9">
+        <v>0</v>
+      </c>
+      <c r="J14" s="9">
+        <v>0</v>
+      </c>
+      <c r="K14" s="9">
+        <v>0</v>
+      </c>
+      <c r="L14" s="9">
+        <v>0</v>
+      </c>
+      <c r="M14" s="9">
+        <v>0</v>
+      </c>
+      <c r="N14" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A15" s="6">
         <v>713</v>
       </c>
-      <c r="B14" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="C14" s="9">
-        <v>1</v>
-      </c>
-      <c r="D14" s="9">
-        <v>1</v>
-      </c>
-      <c r="E14" s="9">
-        <v>1</v>
-      </c>
-      <c r="F14" s="9">
-        <v>0</v>
-      </c>
-      <c r="G14" s="9">
-        <v>0</v>
-      </c>
-      <c r="H14" s="9">
-        <v>0</v>
-      </c>
-      <c r="I14" s="9">
-        <v>0</v>
-      </c>
-      <c r="J14" s="9">
-        <v>0</v>
-      </c>
-      <c r="K14" s="9">
-        <v>0</v>
-      </c>
-      <c r="L14" s="9">
-        <v>0</v>
-      </c>
-      <c r="M14" s="9">
-        <v>0</v>
-      </c>
-      <c r="N14" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" ht="18.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A15" s="6">
+      <c r="B15" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="C15" s="8">
+        <v>0</v>
+      </c>
+      <c r="D15" s="8">
+        <v>0</v>
+      </c>
+      <c r="E15" s="8">
+        <v>0</v>
+      </c>
+      <c r="F15" s="8">
+        <v>0</v>
+      </c>
+      <c r="G15" s="8">
+        <v>0</v>
+      </c>
+      <c r="H15" s="8">
+        <v>0</v>
+      </c>
+      <c r="I15" s="8">
+        <v>0</v>
+      </c>
+      <c r="J15" s="8">
+        <v>0</v>
+      </c>
+      <c r="K15" s="8">
+        <v>0</v>
+      </c>
+      <c r="L15" s="8">
+        <v>0</v>
+      </c>
+      <c r="M15" s="8">
+        <v>0</v>
+      </c>
+      <c r="N15" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A16" s="6">
         <v>714</v>
       </c>
-      <c r="B15" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="C15" s="8">
-        <v>0</v>
-      </c>
-      <c r="D15" s="8">
-        <v>1</v>
-      </c>
-      <c r="E15" s="8">
-        <v>1</v>
-      </c>
-      <c r="F15" s="8">
-        <v>0</v>
-      </c>
-      <c r="G15" s="8">
-        <v>0</v>
-      </c>
-      <c r="H15" s="8">
-        <v>0</v>
-      </c>
-      <c r="I15" s="8">
-        <v>0</v>
-      </c>
-      <c r="J15" s="8">
-        <v>0</v>
-      </c>
-      <c r="K15" s="8">
-        <v>0</v>
-      </c>
-      <c r="L15" s="8">
-        <v>0</v>
-      </c>
-      <c r="M15" s="8">
-        <v>0</v>
-      </c>
-      <c r="N15" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" ht="18.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A16" s="6">
+      <c r="B16" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="C16" s="9">
+        <v>0</v>
+      </c>
+      <c r="D16" s="9">
+        <v>0</v>
+      </c>
+      <c r="E16" s="9">
+        <v>0</v>
+      </c>
+      <c r="F16" s="9">
+        <v>0</v>
+      </c>
+      <c r="G16" s="9">
+        <v>0</v>
+      </c>
+      <c r="H16" s="9">
+        <v>0</v>
+      </c>
+      <c r="I16" s="9">
+        <v>0</v>
+      </c>
+      <c r="J16" s="9">
+        <v>0</v>
+      </c>
+      <c r="K16" s="9">
+        <v>0</v>
+      </c>
+      <c r="L16" s="9">
+        <v>0</v>
+      </c>
+      <c r="M16" s="9">
+        <v>0</v>
+      </c>
+      <c r="N16" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A17" s="6">
         <v>715</v>
       </c>
-      <c r="B16" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="C16" s="9">
-        <v>0</v>
-      </c>
-      <c r="D16" s="9">
-        <v>1</v>
-      </c>
-      <c r="E16" s="9">
-        <v>1</v>
-      </c>
-      <c r="F16" s="9">
-        <v>0</v>
-      </c>
-      <c r="G16" s="9">
-        <v>0</v>
-      </c>
-      <c r="H16" s="9">
-        <v>0</v>
-      </c>
-      <c r="I16" s="9">
-        <v>0</v>
-      </c>
-      <c r="J16" s="9">
-        <v>0</v>
-      </c>
-      <c r="K16" s="9">
-        <v>0</v>
-      </c>
-      <c r="L16" s="9">
-        <v>0</v>
-      </c>
-      <c r="M16" s="9">
-        <v>0</v>
-      </c>
-      <c r="N16" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" ht="18.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A17" s="6">
+      <c r="B17" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C17" s="8">
+        <v>0</v>
+      </c>
+      <c r="D17" s="8">
+        <v>0</v>
+      </c>
+      <c r="E17" s="8">
+        <v>0</v>
+      </c>
+      <c r="F17" s="8">
+        <v>0</v>
+      </c>
+      <c r="G17" s="8">
+        <v>0</v>
+      </c>
+      <c r="H17" s="8">
+        <v>0</v>
+      </c>
+      <c r="I17" s="8">
+        <v>0</v>
+      </c>
+      <c r="J17" s="8">
+        <v>0</v>
+      </c>
+      <c r="K17" s="8">
+        <v>0</v>
+      </c>
+      <c r="L17" s="8">
+        <v>0</v>
+      </c>
+      <c r="M17" s="8">
+        <v>0</v>
+      </c>
+      <c r="N17" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A18" s="6">
         <v>716</v>
       </c>
-      <c r="B17" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="C17" s="8">
-        <v>0</v>
-      </c>
-      <c r="D17" s="8">
-        <v>1</v>
-      </c>
-      <c r="E17" s="8">
-        <v>1</v>
-      </c>
-      <c r="F17" s="8">
-        <v>0</v>
-      </c>
-      <c r="G17" s="8">
-        <v>0</v>
-      </c>
-      <c r="H17" s="8">
-        <v>0</v>
-      </c>
-      <c r="I17" s="8">
-        <v>0</v>
-      </c>
-      <c r="J17" s="8">
-        <v>0</v>
-      </c>
-      <c r="K17" s="8">
-        <v>0</v>
-      </c>
-      <c r="L17" s="8">
-        <v>0</v>
-      </c>
-      <c r="M17" s="8">
-        <v>0</v>
-      </c>
-      <c r="N17" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" ht="18.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A18" s="6">
+      <c r="B18" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C18" s="9">
+        <v>0</v>
+      </c>
+      <c r="D18" s="9">
+        <v>0</v>
+      </c>
+      <c r="E18" s="9">
+        <v>0</v>
+      </c>
+      <c r="F18" s="9">
+        <v>0</v>
+      </c>
+      <c r="G18" s="9">
+        <v>0</v>
+      </c>
+      <c r="H18" s="9">
+        <v>0</v>
+      </c>
+      <c r="I18" s="9">
+        <v>0</v>
+      </c>
+      <c r="J18" s="9">
+        <v>0</v>
+      </c>
+      <c r="K18" s="9">
+        <v>0</v>
+      </c>
+      <c r="L18" s="9">
+        <v>0</v>
+      </c>
+      <c r="M18" s="9">
+        <v>0</v>
+      </c>
+      <c r="N18" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A19" s="6">
         <v>717</v>
       </c>
-      <c r="B18" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="C18" s="9">
-        <v>0</v>
-      </c>
-      <c r="D18" s="9">
-        <v>1</v>
-      </c>
-      <c r="E18" s="9">
-        <v>1</v>
-      </c>
-      <c r="F18" s="9">
-        <v>0</v>
-      </c>
-      <c r="G18" s="9">
-        <v>0</v>
-      </c>
-      <c r="H18" s="9">
-        <v>0</v>
-      </c>
-      <c r="I18" s="9">
-        <v>0</v>
-      </c>
-      <c r="J18" s="9">
-        <v>0</v>
-      </c>
-      <c r="K18" s="9">
-        <v>0</v>
-      </c>
-      <c r="L18" s="9">
-        <v>0</v>
-      </c>
-      <c r="M18" s="9">
-        <v>0</v>
-      </c>
-      <c r="N18" s="9">
+      <c r="B19" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="C19" s="8">
+        <v>0</v>
+      </c>
+      <c r="D19" s="8">
+        <v>0</v>
+      </c>
+      <c r="E19" s="8">
+        <v>0</v>
+      </c>
+      <c r="F19" s="8">
+        <v>0</v>
+      </c>
+      <c r="G19" s="8">
+        <v>0</v>
+      </c>
+      <c r="H19" s="8">
+        <v>0</v>
+      </c>
+      <c r="I19" s="8">
+        <v>0</v>
+      </c>
+      <c r="J19" s="8">
+        <v>0</v>
+      </c>
+      <c r="K19" s="8">
+        <v>0</v>
+      </c>
+      <c r="L19" s="8">
+        <v>0</v>
+      </c>
+      <c r="M19" s="8">
+        <v>0</v>
+      </c>
+      <c r="N19" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A20" s="6">
+        <v>941</v>
+      </c>
+      <c r="B20" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="C20" s="9">
+        <v>0</v>
+      </c>
+      <c r="D20" s="9">
+        <v>0</v>
+      </c>
+      <c r="E20" s="9">
+        <v>0</v>
+      </c>
+      <c r="F20" s="9">
+        <v>0</v>
+      </c>
+      <c r="G20" s="9">
+        <v>0</v>
+      </c>
+      <c r="H20" s="9">
+        <v>0</v>
+      </c>
+      <c r="I20" s="9">
+        <v>0</v>
+      </c>
+      <c r="J20" s="9">
+        <v>0</v>
+      </c>
+      <c r="K20" s="9">
+        <v>0</v>
+      </c>
+      <c r="L20" s="9">
+        <v>0</v>
+      </c>
+      <c r="M20" s="9">
+        <v>0</v>
+      </c>
+      <c r="N20" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A21" s="6">
+        <v>945</v>
+      </c>
+      <c r="B21" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="C21" s="8">
+        <v>0</v>
+      </c>
+      <c r="D21" s="8">
+        <v>0</v>
+      </c>
+      <c r="E21" s="8">
+        <v>0</v>
+      </c>
+      <c r="F21" s="8">
+        <v>0</v>
+      </c>
+      <c r="G21" s="8">
+        <v>0</v>
+      </c>
+      <c r="H21" s="8">
+        <v>0</v>
+      </c>
+      <c r="I21" s="8">
+        <v>0</v>
+      </c>
+      <c r="J21" s="8">
+        <v>0</v>
+      </c>
+      <c r="K21" s="8">
+        <v>0</v>
+      </c>
+      <c r="L21" s="8">
+        <v>0</v>
+      </c>
+      <c r="M21" s="8">
+        <v>0</v>
+      </c>
+      <c r="N21" s="8">
         <v>0</v>
       </c>
     </row>
@@ -1567,7 +1630,7 @@
     <mergeCell ref="A3:B3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
   <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
@@ -1577,89 +1640,94 @@
   <sheetPr>
     <tabColor rgb="FF70AD47"/>
   </sheetPr>
-  <dimension ref="A1:A15"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:A16"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="17.25" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="10" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>10</v>
+        <v>39</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>35</v>
+        <v>11</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>40</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>